--- a/payroll/2026/excel/20260926-0927.xlsx
+++ b/payroll/2026/excel/20260926-0927.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\personal\cqsj\payroll\2026\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA0C0BB-8E72-4B0E-B6AD-BBA02F4097B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0C7D12-998C-42E4-9248-85C70F673F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13305" yWindow="450" windowWidth="32145" windowHeight="20430" activeTab="1" xr2:uid="{7A907552-1C41-4484-ABB7-89D0B7E40110}"/>
+    <workbookView xWindow="11250" yWindow="0" windowWidth="26880" windowHeight="20985" activeTab="1" xr2:uid="{7A907552-1C41-4484-ABB7-89D0B7E40110}"/>
   </bookViews>
   <sheets>
     <sheet name="产出" sheetId="4" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
   <si>
     <t>人员</t>
   </si>
@@ -532,9 +532,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -547,11 +544,64 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -906,7 +956,7 @@
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="70.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23" style="2" customWidth="1"/>
-    <col min="2" max="2" width="45.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="47.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="28" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="12.375" style="1" customWidth="1"/>
@@ -1051,724 +1101,707 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A76FA64F-2994-4A17-8B67-4FDBD51AF35E}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultColWidth="21.75" defaultRowHeight="57.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="17.25" style="10" customWidth="1"/>
-    <col min="3" max="3" width="12.75" style="10" customWidth="1"/>
-    <col min="4" max="4" width="9.75" style="10" customWidth="1"/>
-    <col min="5" max="5" width="20.625" style="10" customWidth="1"/>
-    <col min="6" max="6" width="21.25" style="10" customWidth="1"/>
-    <col min="7" max="7" width="20" style="10" customWidth="1"/>
-    <col min="8" max="8" width="29.125" style="10" customWidth="1"/>
-    <col min="9" max="16384" width="21.75" style="10"/>
+    <col min="2" max="2" width="17.25" style="9" customWidth="1"/>
+    <col min="3" max="3" width="12.75" style="9" customWidth="1"/>
+    <col min="4" max="4" width="9.75" style="9" customWidth="1"/>
+    <col min="5" max="5" width="20.625" style="9" customWidth="1"/>
+    <col min="6" max="6" width="21.25" style="9" customWidth="1"/>
+    <col min="7" max="7" width="20" style="9" customWidth="1"/>
+    <col min="8" max="8" width="29.125" style="9" customWidth="1"/>
+    <col min="9" max="16384" width="21.75" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="57.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="10" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13">
+    <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="11">
         <f>E3+F3+G3+H3</f>
         <v>353</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12">
-        <v>65</v>
-      </c>
-      <c r="F3" s="12">
-        <v>44</v>
-      </c>
-      <c r="G3" s="12">
+      <c r="D3" s="11"/>
+      <c r="E3" s="11">
+        <v>65</v>
+      </c>
+      <c r="F3" s="11">
+        <v>44</v>
+      </c>
+      <c r="G3" s="11">
         <v>89</v>
       </c>
-      <c r="H3" s="12">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="H3" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
         <v>2</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="12">
-        <f t="shared" ref="C4:C33" si="0">E4+F4+G4+H4</f>
-        <v>65</v>
-      </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12">
-        <v>65</v>
-      </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-    </row>
-    <row r="5" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13">
+      <c r="C4" s="11">
+        <f t="shared" ref="C4:C32" si="0">E4+F4+G4+H4</f>
+        <v>65</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11">
+        <v>65</v>
+      </c>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="12">
         <v>3</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <f t="shared" si="0"/>
         <v>220</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12">
-        <v>65</v>
-      </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13">
+      <c r="D5" s="11"/>
+      <c r="E5" s="11">
+        <v>65</v>
+      </c>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
         <v>4</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <f t="shared" si="0"/>
         <v>198</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12">
-        <v>65</v>
-      </c>
-      <c r="F6" s="12">
-        <v>44</v>
-      </c>
-      <c r="G6" s="12">
+      <c r="D6" s="11"/>
+      <c r="E6" s="11">
+        <v>65</v>
+      </c>
+      <c r="F6" s="11">
+        <v>44</v>
+      </c>
+      <c r="G6" s="11">
         <v>89</v>
       </c>
-      <c r="H6" s="12"/>
-    </row>
-    <row r="7" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13">
+      <c r="H6" s="11"/>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
         <v>5</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <f t="shared" si="0"/>
         <v>353</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12">
-        <v>65</v>
-      </c>
-      <c r="F7" s="12">
-        <v>44</v>
-      </c>
-      <c r="G7" s="12">
+      <c r="D7" s="11"/>
+      <c r="E7" s="11">
+        <v>65</v>
+      </c>
+      <c r="F7" s="11">
+        <v>44</v>
+      </c>
+      <c r="G7" s="11">
         <v>89</v>
       </c>
-      <c r="H7" s="12">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13">
+      <c r="H7" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
         <v>6</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <f t="shared" si="0"/>
         <v>198</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12">
-        <v>65</v>
-      </c>
-      <c r="F8" s="12">
-        <v>44</v>
-      </c>
-      <c r="G8" s="12">
+      <c r="D8" s="11"/>
+      <c r="E8" s="11">
+        <v>65</v>
+      </c>
+      <c r="F8" s="11">
+        <v>44</v>
+      </c>
+      <c r="G8" s="11">
         <v>89</v>
       </c>
-      <c r="H8" s="12"/>
-    </row>
-    <row r="9" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13">
+      <c r="H8" s="11"/>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
         <v>7</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="11">
         <f t="shared" si="0"/>
         <v>353</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12">
-        <v>65</v>
-      </c>
-      <c r="F9" s="12">
-        <v>44</v>
-      </c>
-      <c r="G9" s="12">
+      <c r="D9" s="11"/>
+      <c r="E9" s="11">
+        <v>65</v>
+      </c>
+      <c r="F9" s="11">
+        <v>44</v>
+      </c>
+      <c r="G9" s="11">
         <v>89</v>
       </c>
-      <c r="H9" s="12">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13">
+      <c r="H9" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
         <v>8</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="11">
         <f t="shared" si="0"/>
         <v>109</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12">
-        <v>65</v>
-      </c>
-      <c r="F10" s="12">
-        <v>44</v>
-      </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-    </row>
-    <row r="11" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13">
+      <c r="D10" s="11"/>
+      <c r="E10" s="11">
+        <v>65</v>
+      </c>
+      <c r="F10" s="11">
+        <v>44</v>
+      </c>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12">
         <v>9</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="12">
-        <f t="shared" si="0"/>
-        <v>65</v>
-      </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12">
-        <v>65</v>
-      </c>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-    </row>
-    <row r="12" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13">
+      <c r="C11" s="11">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11">
+        <v>65</v>
+      </c>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12">
         <v>10</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="11">
         <f t="shared" si="0"/>
         <v>353</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12">
-        <v>65</v>
-      </c>
-      <c r="F12" s="12">
-        <v>44</v>
-      </c>
-      <c r="G12" s="12">
+      <c r="D12" s="11"/>
+      <c r="E12" s="11">
+        <v>65</v>
+      </c>
+      <c r="F12" s="11">
+        <v>44</v>
+      </c>
+      <c r="G12" s="11">
         <v>89</v>
       </c>
-      <c r="H12" s="12">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="13">
+      <c r="H12" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
         <v>11</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <f t="shared" si="0"/>
         <v>220</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12">
-        <v>65</v>
-      </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13">
+      <c r="D13" s="11"/>
+      <c r="E13" s="11">
+        <v>65</v>
+      </c>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
         <v>12</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <f t="shared" si="0"/>
         <v>154</v>
       </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12">
-        <v>65</v>
-      </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12">
+      <c r="D14" s="11"/>
+      <c r="E14" s="11">
+        <v>65</v>
+      </c>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11">
         <v>89</v>
       </c>
-      <c r="H14" s="12"/>
-    </row>
-    <row r="15" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13">
+      <c r="H14" s="11"/>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12">
         <v>13</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <v>28</v>
       </c>
-      <c r="C15" s="12">
-        <f t="shared" si="0"/>
-        <v>65</v>
-      </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12">
-        <v>65</v>
-      </c>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-    </row>
-    <row r="16" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="13">
+      <c r="C15" s="11">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11">
+        <v>65</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12">
         <v>14</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="11">
         <f t="shared" si="0"/>
         <v>264</v>
       </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12">
-        <v>65</v>
-      </c>
-      <c r="F16" s="12">
-        <v>44</v>
-      </c>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="13">
+      <c r="D16" s="11"/>
+      <c r="E16" s="11">
+        <v>65</v>
+      </c>
+      <c r="F16" s="11">
+        <v>44</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12">
         <v>15</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="11">
         <f t="shared" si="0"/>
         <v>109</v>
       </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12">
-        <v>65</v>
-      </c>
-      <c r="F17" s="12">
-        <v>44</v>
-      </c>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-    </row>
-    <row r="18" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="13">
+      <c r="D17" s="11"/>
+      <c r="E17" s="11">
+        <v>65</v>
+      </c>
+      <c r="F17" s="11">
+        <v>44</v>
+      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+    </row>
+    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12">
         <v>16</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="11">
+        <f t="shared" si="0"/>
+        <v>353</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11">
+        <v>65</v>
+      </c>
+      <c r="F18" s="11">
+        <v>44</v>
+      </c>
+      <c r="G18" s="11">
+        <v>89</v>
+      </c>
+      <c r="H18" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12">
+        <v>17</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="11">
+        <f t="shared" si="0"/>
+        <v>309</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11">
+        <v>65</v>
+      </c>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11">
+        <v>89</v>
+      </c>
+      <c r="H19" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12">
+        <v>18</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="11">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11">
+        <v>44</v>
+      </c>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+    </row>
+    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="11">
+        <f t="shared" si="0"/>
+        <v>244</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11">
+        <v>89</v>
+      </c>
+      <c r="H21" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12">
+        <v>20</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="12">
-        <f t="shared" si="0"/>
-        <v>65</v>
-      </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12">
-        <v>65</v>
-      </c>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-    </row>
-    <row r="19" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13">
+      <c r="C22" s="11">
+        <f t="shared" si="0"/>
+        <v>264</v>
+      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11">
+        <v>65</v>
+      </c>
+      <c r="F22" s="11">
+        <v>44</v>
+      </c>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="12">
+        <v>21</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="11">
+        <f t="shared" si="0"/>
+        <v>288</v>
+      </c>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11">
+        <v>44</v>
+      </c>
+      <c r="G23" s="11">
+        <v>89</v>
+      </c>
+      <c r="H23" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12">
+        <v>22</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="11">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11">
+        <v>44</v>
+      </c>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+    </row>
+    <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12">
+        <v>23</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="11">
+        <f t="shared" si="0"/>
+        <v>133</v>
+      </c>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11">
+        <v>44</v>
+      </c>
+      <c r="G25" s="11">
+        <v>89</v>
+      </c>
+      <c r="H25" s="11"/>
+    </row>
+    <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12">
+        <v>24</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="12">
-        <f t="shared" si="0"/>
-        <v>353</v>
-      </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12">
-        <v>65</v>
-      </c>
-      <c r="F19" s="12">
-        <v>44</v>
-      </c>
-      <c r="G19" s="12">
+      <c r="C26" s="11">
+        <f t="shared" si="0"/>
+        <v>133</v>
+      </c>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11">
+        <v>44</v>
+      </c>
+      <c r="G26" s="11">
         <v>89</v>
       </c>
-      <c r="H19" s="12">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13">
-        <v>18</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="12">
-        <f t="shared" si="0"/>
-        <v>309</v>
-      </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12">
-        <v>65</v>
-      </c>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12">
+      <c r="H26" s="11"/>
+    </row>
+    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="12">
+        <v>25</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="11">
+        <f t="shared" si="0"/>
+        <v>133</v>
+      </c>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11">
+        <v>44</v>
+      </c>
+      <c r="G27" s="11">
         <v>89</v>
       </c>
-      <c r="H20" s="12">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13">
-        <v>19</v>
-      </c>
-      <c r="B21" s="12" t="s">
+      <c r="H27" s="11"/>
+    </row>
+    <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12">
         <v>26</v>
       </c>
-      <c r="C21" s="12">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12">
-        <v>44</v>
-      </c>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-    </row>
-    <row r="22" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13">
-        <v>20</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="12">
+      <c r="B28" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="11">
         <f t="shared" si="0"/>
         <v>244</v>
       </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12">
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11">
         <v>89</v>
       </c>
-      <c r="H22" s="12">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="13">
-        <v>21</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="12">
-        <f t="shared" si="0"/>
-        <v>199</v>
-      </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12">
-        <v>44</v>
-      </c>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="13">
+      <c r="H28" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="12">
+        <v>27</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="11">
+        <f t="shared" si="0"/>
+        <v>155</v>
+      </c>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="12">
+        <v>28</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="11">
+        <f t="shared" si="0"/>
+        <v>155</v>
+      </c>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="12">
+        <v>29</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="12">
-        <f t="shared" si="0"/>
-        <v>288</v>
-      </c>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12">
-        <v>44</v>
-      </c>
-      <c r="G24" s="12">
-        <v>89</v>
-      </c>
-      <c r="H24" s="12">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="13">
-        <v>23</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="12">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12">
-        <v>44</v>
-      </c>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-    </row>
-    <row r="26" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="13">
-        <v>24</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="12">
-        <f t="shared" si="0"/>
-        <v>133</v>
-      </c>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12">
-        <v>44</v>
-      </c>
-      <c r="G26" s="12">
-        <v>89</v>
-      </c>
-      <c r="H26" s="12"/>
-    </row>
-    <row r="27" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="13">
-        <v>25</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="12">
-        <f t="shared" si="0"/>
-        <v>133</v>
-      </c>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12">
-        <v>44</v>
-      </c>
-      <c r="G27" s="12">
-        <v>89</v>
-      </c>
-      <c r="H27" s="12"/>
-    </row>
-    <row r="28" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="13">
-        <v>26</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="12">
-        <f t="shared" si="0"/>
-        <v>133</v>
-      </c>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12">
-        <v>44</v>
-      </c>
-      <c r="G28" s="12">
-        <v>89</v>
-      </c>
-      <c r="H28" s="12"/>
-    </row>
-    <row r="29" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="13">
-        <v>27</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="12">
-        <f t="shared" si="0"/>
-        <v>244</v>
-      </c>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12">
-        <v>89</v>
-      </c>
-      <c r="H29" s="12">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="13">
-        <v>28</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="12">
-        <f t="shared" si="0"/>
-        <v>155</v>
-      </c>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="13">
-        <v>29</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="12">
-        <f t="shared" si="0"/>
-        <v>155</v>
-      </c>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="13">
+      <c r="C31" s="11">
+        <f t="shared" si="0"/>
+        <v>155</v>
+      </c>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12">
         <v>30</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" s="12">
-        <f t="shared" si="0"/>
-        <v>155</v>
-      </c>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="13">
-        <v>31</v>
-      </c>
-      <c r="B33" s="12" t="s">
+      <c r="B32" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="12">
-        <f t="shared" si="0"/>
-        <v>155</v>
-      </c>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="8" t="s">
+      <c r="C32" s="11">
+        <f t="shared" si="0"/>
+        <v>155</v>
+      </c>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="8">
-        <f>SUM(C3:C33)</f>
+      <c r="C33" s="8">
+        <f>SUM(C3:C32)</f>
         <v>5888</v>
       </c>
     </row>
@@ -1777,11 +1810,14 @@
     <mergeCell ref="B1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B34:B1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  <conditionalFormatting sqref="B33:B1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/payroll/2026/excel/20260926-0927.xlsx
+++ b/payroll/2026/excel/20260926-0927.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\personal\cqsj\payroll\2026\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0C7D12-998C-42E4-9248-85C70F673F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D343F79-723D-44B5-9C40-42FFC09DD3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11250" yWindow="0" windowWidth="26880" windowHeight="20985" activeTab="1" xr2:uid="{7A907552-1C41-4484-ABB7-89D0B7E40110}"/>
   </bookViews>
